--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.01708279317776</v>
+        <v>2.115275953891386</v>
       </c>
       <c r="D2" t="n">
-        <v>11.77173121086635</v>
+        <v>1.912906321765782</v>
       </c>
       <c r="E2" t="n">
-        <v>13.68467423545833</v>
+        <v>2.223759563261978</v>
       </c>
       <c r="F2" t="n">
-        <v>13.71052503773308</v>
+        <v>2.227960318631626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.94589533299273</v>
+        <v>6.653707991611319</v>
       </c>
       <c r="D3" t="n">
-        <v>43.2507651355124</v>
+        <v>7.028249334520766</v>
       </c>
       <c r="E3" t="n">
-        <v>13.68467423545833</v>
+        <v>2.223759563261978</v>
       </c>
       <c r="F3" t="n">
-        <v>13.71052503773308</v>
+        <v>2.227960318631626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.03460286616662</v>
+        <v>6.993122965752076</v>
       </c>
       <c r="D4" t="n">
-        <v>37.64564766327329</v>
+        <v>6.11741774528191</v>
       </c>
       <c r="E4" t="n">
-        <v>13.68467423545833</v>
+        <v>2.223759563261978</v>
       </c>
       <c r="F4" t="n">
-        <v>13.71052503773308</v>
+        <v>2.227960318631626</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
